--- a/Document/客户方案计算表(2)(1).xlsx
+++ b/Document/客户方案计算表(2)(1).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9564"/>
+    <workbookView windowWidth="30720" windowHeight="14340"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>使用说明</t>
   </si>
@@ -140,14 +140,20 @@
   <si>
     <t>第二期计息本金=客户实际到账本金-应抵本金</t>
   </si>
+  <si>
+    <t>最大减免</t>
+  </si>
+  <si>
+    <t xml:space="preserve">合同金额180000 -本金100000 -36期利息 </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
@@ -186,7 +192,68 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -209,14 +276,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,6 +284,29 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -231,14 +314,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -252,83 +335,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
@@ -357,181 +363,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -560,6 +566,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -571,35 +586,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -622,8 +608,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -657,6 +643,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -665,10 +671,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -677,133 +683,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1195,7 +1201,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1255,48 +1261,48 @@
       <c r="J2" s="12"/>
       <c r="K2" s="12"/>
     </row>
-    <row r="3" spans="2:9">
+    <row r="3" ht="28.8" spans="2:9">
       <c r="B3" s="8">
-        <v>250000</v>
+        <v>100000</v>
       </c>
       <c r="C3" s="7">
         <v>1</v>
       </c>
       <c r="D3" s="9">
         <f>B3*15.4%/12</f>
-        <v>3208.33333333333</v>
+        <v>1283.33333333333</v>
       </c>
       <c r="E3" s="10">
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F3" s="9">
         <f>E3-D3</f>
-        <v>5874.97666666667</v>
+        <v>3716.66666666667</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" spans="2:9">
+    <row r="4" ht="43.2" spans="2:9">
       <c r="B4" s="9">
         <f>B3-F3</f>
-        <v>244125.023333333</v>
+        <v>96283.3333333333</v>
       </c>
       <c r="C4" s="7">
         <v>2</v>
       </c>
       <c r="D4" s="9">
         <f t="shared" ref="D4:D22" si="0">B4*15.4%/12</f>
-        <v>3132.93779944444</v>
+        <v>1235.63611111111</v>
       </c>
       <c r="E4" s="11">
         <f>$E$3</f>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F4" s="9">
         <f t="shared" ref="F4:F22" si="1">E4-D4</f>
-        <v>5950.37220055556</v>
+        <v>3764.36388888889</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>14</v>
@@ -1305,75 +1311,75 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" ht="28.8" spans="2:9">
       <c r="B5" s="9">
         <f t="shared" ref="B5:B22" si="2">B4-F4</f>
-        <v>238174.651132778</v>
+        <v>92518.9694444444</v>
       </c>
       <c r="C5" s="7">
         <v>3</v>
       </c>
       <c r="D5" s="9">
         <f t="shared" si="0"/>
-        <v>3056.57468953732</v>
+        <v>1187.32677453704</v>
       </c>
       <c r="E5" s="11">
         <f t="shared" ref="E5:E14" si="3">$E$3</f>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F5" s="9">
         <f t="shared" si="1"/>
-        <v>6026.73531046268</v>
+        <v>3812.67322546296</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="2:9">
+    <row r="6" ht="28.8" spans="2:9">
       <c r="B6" s="9">
         <f t="shared" si="2"/>
-        <v>232147.915822315</v>
+        <v>88706.2962189815</v>
       </c>
       <c r="C6" s="7">
         <v>4</v>
       </c>
       <c r="D6" s="9">
         <f t="shared" si="0"/>
-        <v>2979.23158638638</v>
+        <v>1138.3974681436</v>
       </c>
       <c r="E6" s="11">
         <f t="shared" si="3"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F6" s="9">
         <f t="shared" si="1"/>
-        <v>6104.07841361362</v>
+        <v>3861.6025318564</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="7"/>
     </row>
-    <row r="7" spans="2:9">
+    <row r="7" ht="28.8" spans="2:9">
       <c r="B7" s="9">
         <f t="shared" si="2"/>
-        <v>226043.837408701</v>
+        <v>84844.6936871251</v>
       </c>
       <c r="C7" s="7">
         <v>5</v>
       </c>
       <c r="D7" s="9">
         <f t="shared" si="0"/>
-        <v>2900.89591341167</v>
+        <v>1088.84023565144</v>
       </c>
       <c r="E7" s="11">
         <f t="shared" si="3"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F7" s="9">
         <f t="shared" si="1"/>
-        <v>6182.41408658833</v>
+        <v>3911.15976434856</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>18</v>
@@ -1383,652 +1389,683 @@
     <row r="8" spans="2:6">
       <c r="B8" s="9">
         <f t="shared" si="2"/>
-        <v>219861.423322113</v>
+        <v>80933.5339227765</v>
       </c>
       <c r="C8" s="7">
         <v>6</v>
       </c>
       <c r="D8" s="9">
         <f t="shared" si="0"/>
-        <v>2821.55493263379</v>
+        <v>1038.64701867563</v>
       </c>
       <c r="E8" s="11">
         <f t="shared" si="3"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F8" s="9">
         <f t="shared" si="1"/>
-        <v>6261.75506736621</v>
+        <v>3961.35298132437</v>
       </c>
     </row>
     <row r="9" spans="2:6">
       <c r="B9" s="9">
         <f t="shared" si="2"/>
-        <v>213599.668254747</v>
+        <v>76972.1809414521</v>
       </c>
       <c r="C9" s="7">
         <v>7</v>
       </c>
       <c r="D9" s="9">
         <f t="shared" si="0"/>
-        <v>2741.19574260259</v>
+        <v>987.809655415302</v>
       </c>
       <c r="E9" s="11">
         <f t="shared" si="3"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F9" s="9">
         <f t="shared" si="1"/>
-        <v>6342.11425739741</v>
+        <v>4012.1903445847</v>
       </c>
     </row>
     <row r="10" spans="2:6">
       <c r="B10" s="9">
         <f t="shared" si="2"/>
-        <v>207257.55399735</v>
+        <v>72959.9905968674</v>
       </c>
       <c r="C10" s="7">
         <v>8</v>
       </c>
       <c r="D10" s="9">
         <f t="shared" si="0"/>
-        <v>2659.80527629932</v>
+        <v>936.319879326466</v>
       </c>
       <c r="E10" s="11">
         <f t="shared" si="3"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F10" s="9">
         <f t="shared" si="1"/>
-        <v>6423.50472370068</v>
+        <v>4063.68012067353</v>
       </c>
     </row>
     <row r="11" spans="2:6">
       <c r="B11" s="9">
         <f t="shared" si="2"/>
-        <v>200834.049273649</v>
+        <v>68896.3104761939</v>
       </c>
       <c r="C11" s="7">
         <v>9</v>
       </c>
       <c r="D11" s="9">
         <f t="shared" si="0"/>
-        <v>2577.37029901183</v>
+        <v>884.169317777822</v>
       </c>
       <c r="E11" s="11">
         <f t="shared" si="3"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F11" s="9">
         <f t="shared" si="1"/>
-        <v>6505.93970098817</v>
+        <v>4115.83068222218</v>
       </c>
     </row>
     <row r="12" spans="2:6">
       <c r="B12" s="9">
         <f t="shared" si="2"/>
-        <v>194328.109572661</v>
+        <v>64780.4797939717</v>
       </c>
       <c r="C12" s="7">
         <v>10</v>
       </c>
       <c r="D12" s="9">
         <f t="shared" si="0"/>
-        <v>2493.87740618248</v>
+        <v>831.349490689304</v>
       </c>
       <c r="E12" s="11">
         <f t="shared" si="3"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F12" s="9">
         <f t="shared" si="1"/>
-        <v>6589.43259381752</v>
+        <v>4168.6505093107</v>
       </c>
     </row>
     <row r="13" spans="2:6">
       <c r="B13" s="9">
         <f t="shared" si="2"/>
-        <v>187738.676978843</v>
+        <v>60611.829284661</v>
       </c>
       <c r="C13" s="7">
         <v>11</v>
       </c>
       <c r="D13" s="9">
         <f t="shared" si="0"/>
-        <v>2409.31302122849</v>
+        <v>777.85180915315</v>
       </c>
       <c r="E13" s="11">
         <f t="shared" si="3"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F13" s="9">
         <f t="shared" si="1"/>
-        <v>6673.99697877151</v>
+        <v>4222.14819084685</v>
       </c>
     </row>
     <row r="14" spans="2:6">
       <c r="B14" s="9">
         <f t="shared" si="2"/>
-        <v>181064.680000072</v>
+        <v>56389.6810938142</v>
       </c>
       <c r="C14" s="7">
         <v>12</v>
       </c>
       <c r="D14" s="9">
         <f t="shared" si="0"/>
-        <v>2323.66339333425</v>
+        <v>723.667574037282</v>
       </c>
       <c r="E14" s="11">
         <f t="shared" si="3"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F14" s="9">
         <f t="shared" si="1"/>
-        <v>6759.64660666575</v>
+        <v>4276.33242596272</v>
       </c>
     </row>
     <row r="15" spans="2:6">
       <c r="B15" s="9">
         <f t="shared" si="2"/>
-        <v>174305.033393406</v>
+        <v>52113.3486678515</v>
       </c>
       <c r="C15" s="7">
         <v>13</v>
       </c>
       <c r="D15" s="9">
         <f t="shared" si="0"/>
-        <v>2236.91459521537</v>
+        <v>668.78797457076</v>
       </c>
       <c r="E15" s="11">
         <f t="shared" ref="E15:E24" si="4">$E$3</f>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F15" s="9">
         <f t="shared" si="1"/>
-        <v>6846.39540478462</v>
+        <v>4331.21202542924</v>
       </c>
     </row>
     <row r="16" spans="2:6">
       <c r="B16" s="9">
         <f t="shared" si="2"/>
-        <v>167458.637988621</v>
+        <v>47782.1366424222</v>
       </c>
       <c r="C16" s="7">
         <v>14</v>
       </c>
       <c r="D16" s="9">
         <f t="shared" si="0"/>
-        <v>2149.05252085397</v>
+        <v>613.204086911085</v>
       </c>
       <c r="E16" s="11">
         <f t="shared" si="4"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F16" s="9">
         <f t="shared" si="1"/>
-        <v>6934.25747914603</v>
+        <v>4386.79591308891</v>
       </c>
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="9">
         <f t="shared" si="2"/>
-        <v>160524.380509475</v>
+        <v>43395.3407293333</v>
       </c>
       <c r="C17" s="7">
         <v>15</v>
       </c>
       <c r="D17" s="9">
         <f t="shared" si="0"/>
-        <v>2060.06288320493</v>
+        <v>556.906872693111</v>
       </c>
       <c r="E17" s="11">
         <f t="shared" si="4"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F17" s="9">
         <f t="shared" si="1"/>
-        <v>7023.24711679507</v>
+        <v>4443.09312730689</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="9">
         <f t="shared" si="2"/>
-        <v>153501.13339268</v>
+        <v>38952.2476020264</v>
       </c>
       <c r="C18" s="7">
         <v>16</v>
       </c>
       <c r="D18" s="9">
         <f t="shared" si="0"/>
-        <v>1969.93121187273</v>
+        <v>499.887177559339</v>
       </c>
       <c r="E18" s="11">
         <f t="shared" si="4"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F18" s="9">
         <f t="shared" si="1"/>
-        <v>7113.37878812727</v>
+        <v>4500.11282244066</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="9">
         <f t="shared" si="2"/>
-        <v>146387.754604553</v>
+        <v>34452.1347795858</v>
       </c>
       <c r="C19" s="7">
         <v>17</v>
       </c>
       <c r="D19" s="9">
         <f t="shared" si="0"/>
-        <v>1878.64285075843</v>
+        <v>442.13572967135</v>
       </c>
       <c r="E19" s="11">
         <f t="shared" si="4"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F19" s="9">
         <f t="shared" si="1"/>
-        <v>7204.66714924157</v>
+        <v>4557.86427032865</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="9">
         <f t="shared" si="2"/>
-        <v>139183.087455311</v>
+        <v>29894.2705092571</v>
       </c>
       <c r="C20" s="7">
         <v>18</v>
       </c>
       <c r="D20" s="9">
         <f t="shared" si="0"/>
-        <v>1786.18295567649</v>
+        <v>383.643138202133</v>
       </c>
       <c r="E20" s="11">
         <f t="shared" si="4"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F20" s="9">
         <f t="shared" si="1"/>
-        <v>7297.12704432351</v>
+        <v>4616.35686179787</v>
       </c>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="9">
         <f t="shared" si="2"/>
-        <v>131885.960410988</v>
+        <v>25277.9136474592</v>
       </c>
       <c r="C21" s="7">
         <v>19</v>
       </c>
       <c r="D21" s="9">
         <f t="shared" si="0"/>
-        <v>1692.53649194101</v>
+        <v>324.39989180906</v>
       </c>
       <c r="E21" s="11">
         <f t="shared" si="4"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F21" s="9">
         <f t="shared" si="1"/>
-        <v>7390.77350805899</v>
+        <v>4675.60010819094</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="9">
         <f t="shared" si="2"/>
-        <v>124495.186902929</v>
+        <v>20602.3135392683</v>
       </c>
       <c r="C22" s="7">
         <v>20</v>
       </c>
       <c r="D22" s="9">
         <f t="shared" si="0"/>
-        <v>1597.68823192092</v>
+        <v>264.396357087276</v>
       </c>
       <c r="E22" s="11">
         <f t="shared" si="4"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F22" s="9">
         <f t="shared" si="1"/>
-        <v>7485.62176807908</v>
+        <v>4735.60364291272</v>
       </c>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="9">
         <f t="shared" ref="B23:B38" si="5">B22-F22</f>
-        <v>117009.56513485</v>
+        <v>15866.7098963556</v>
       </c>
       <c r="C23" s="7">
         <v>21</v>
       </c>
       <c r="D23" s="9">
         <f t="shared" ref="D23:D38" si="6">B23*15.4%/12</f>
-        <v>1501.6227525639</v>
+        <v>203.62277700323</v>
       </c>
       <c r="E23" s="11">
         <f t="shared" si="4"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F23" s="9">
         <f t="shared" ref="F23:F38" si="7">E23-D23</f>
-        <v>7581.6872474361</v>
+        <v>4796.37722299677</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="9">
         <f t="shared" si="5"/>
-        <v>109427.877887414</v>
+        <v>11070.3326733588</v>
       </c>
       <c r="C24" s="7">
         <v>22</v>
       </c>
       <c r="D24" s="9">
         <f t="shared" si="6"/>
-        <v>1404.32443288847</v>
+        <v>142.069269308105</v>
       </c>
       <c r="E24" s="11">
         <f t="shared" si="4"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F24" s="9">
         <f t="shared" si="7"/>
-        <v>7678.98556711153</v>
+        <v>4857.9307306919</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="9">
         <f t="shared" si="5"/>
-        <v>101748.892320302</v>
+        <v>6212.40194266691</v>
       </c>
       <c r="C25" s="7">
         <v>23</v>
       </c>
       <c r="D25" s="9">
         <f t="shared" si="6"/>
-        <v>1305.77745144388</v>
+        <v>79.725824930892</v>
       </c>
       <c r="E25" s="11">
         <f t="shared" ref="E25:E38" si="8">$E$3</f>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F25" s="9">
         <f t="shared" si="7"/>
-        <v>7777.53254855612</v>
+        <v>4920.27417506911</v>
       </c>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="9">
         <f t="shared" si="5"/>
-        <v>93971.3597717459</v>
+        <v>1292.1277675978</v>
       </c>
       <c r="C26" s="7">
         <v>24</v>
       </c>
       <c r="D26" s="9">
         <f t="shared" si="6"/>
-        <v>1205.96578373741</v>
+        <v>16.5823063508384</v>
       </c>
       <c r="E26" s="11">
         <f t="shared" si="8"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F26" s="9">
         <f t="shared" si="7"/>
-        <v>7877.34421626259</v>
+        <v>4983.41769364916</v>
       </c>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="9">
         <f t="shared" si="5"/>
-        <v>86094.0155554833</v>
+        <v>-3691.28992605136</v>
       </c>
       <c r="C27" s="7">
         <v>25</v>
       </c>
       <c r="D27" s="9">
         <f t="shared" si="6"/>
-        <v>1104.8731996287</v>
+        <v>-47.3715540509925</v>
       </c>
       <c r="E27" s="11">
         <f t="shared" si="8"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F27" s="9">
         <f t="shared" si="7"/>
-        <v>7978.4368003713</v>
+        <v>5047.37155405099</v>
       </c>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="9">
         <f t="shared" si="5"/>
-        <v>78115.578755112</v>
+        <v>-8738.66148010235</v>
       </c>
       <c r="C28" s="7">
         <v>26</v>
       </c>
       <c r="D28" s="9">
         <f t="shared" si="6"/>
-        <v>1002.4832606906</v>
+        <v>-112.146155661314</v>
       </c>
       <c r="E28" s="11">
         <f t="shared" si="8"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F28" s="9">
         <f t="shared" si="7"/>
-        <v>8080.82673930939</v>
+        <v>5112.14615566131</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="9">
         <f t="shared" si="5"/>
-        <v>70034.7520158026</v>
+        <v>-13850.8076357637</v>
       </c>
       <c r="C29" s="7">
         <v>27</v>
       </c>
       <c r="D29" s="9">
         <f t="shared" si="6"/>
-        <v>898.779317536134</v>
+        <v>-177.752031325634</v>
       </c>
       <c r="E29" s="11">
         <f t="shared" si="8"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F29" s="9">
         <f t="shared" si="7"/>
-        <v>8184.53068246387</v>
+        <v>5177.75203132563</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="9">
         <f t="shared" si="5"/>
-        <v>61850.2213333388</v>
+        <v>-19028.5596670893</v>
       </c>
       <c r="C30" s="7">
         <v>28</v>
       </c>
       <c r="D30" s="9">
         <f t="shared" si="6"/>
-        <v>793.744507111181</v>
+        <v>-244.199849060979</v>
       </c>
       <c r="E30" s="11">
         <f t="shared" si="8"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F30" s="9">
         <f t="shared" si="7"/>
-        <v>8289.56549288882</v>
+        <v>5244.19984906098</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="9">
         <f t="shared" si="5"/>
-        <v>53560.65584045</v>
+        <v>-24272.7595161503</v>
       </c>
       <c r="C31" s="7">
         <v>29</v>
       </c>
       <c r="D31" s="9">
         <f t="shared" si="6"/>
-        <v>687.361749952441</v>
+        <v>-311.500413790595</v>
       </c>
       <c r="E31" s="11">
         <f t="shared" si="8"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F31" s="9">
         <f t="shared" si="7"/>
-        <v>8395.94825004756</v>
+        <v>5311.5004137906</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="9">
         <f t="shared" si="5"/>
-        <v>45164.7075904024</v>
+        <v>-29584.2599299409</v>
       </c>
       <c r="C32" s="7">
         <v>30</v>
       </c>
       <c r="D32" s="9">
         <f t="shared" si="6"/>
-        <v>579.613747410164</v>
+        <v>-379.664669100908</v>
       </c>
       <c r="E32" s="11">
         <f t="shared" si="8"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F32" s="9">
         <f t="shared" si="7"/>
-        <v>8503.69625258984</v>
+        <v>5379.66466910091</v>
       </c>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="9">
         <f t="shared" si="5"/>
-        <v>36661.0113378126</v>
+        <v>-34963.9245990418</v>
       </c>
       <c r="C33" s="7">
         <v>31</v>
       </c>
       <c r="D33" s="9">
         <f t="shared" si="6"/>
-        <v>470.482978835261</v>
+        <v>-448.703699021036</v>
       </c>
       <c r="E33" s="11">
         <f t="shared" si="8"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F33" s="9">
         <f t="shared" si="7"/>
-        <v>8612.82702116474</v>
+        <v>5448.70369902104</v>
       </c>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="9">
         <f t="shared" si="5"/>
-        <v>28048.1843166478</v>
+        <v>-40412.6282980628</v>
       </c>
       <c r="C34" s="7">
         <v>32</v>
       </c>
       <c r="D34" s="9">
         <f t="shared" si="6"/>
-        <v>359.951698730314</v>
+        <v>-518.628729825139</v>
       </c>
       <c r="E34" s="11">
         <f t="shared" si="8"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F34" s="9">
         <f t="shared" si="7"/>
-        <v>8723.35830126969</v>
+        <v>5518.62872982514</v>
       </c>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="9">
         <f t="shared" si="5"/>
-        <v>19324.8260153781</v>
+        <v>-45931.257027888</v>
       </c>
       <c r="C35" s="7">
         <v>33</v>
       </c>
       <c r="D35" s="9">
         <f t="shared" si="6"/>
-        <v>248.00193386402</v>
+        <v>-589.451131857895</v>
       </c>
       <c r="E35" s="11">
         <f t="shared" si="8"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F35" s="9">
         <f t="shared" si="7"/>
-        <v>8835.30806613598</v>
+        <v>5589.4511318579</v>
       </c>
     </row>
     <row r="36" spans="2:6">
       <c r="B36" s="9">
         <f t="shared" si="5"/>
-        <v>10489.5179492422</v>
+        <v>-51520.7081597459</v>
       </c>
       <c r="C36" s="7">
         <v>34</v>
       </c>
       <c r="D36" s="9">
         <f t="shared" si="6"/>
-        <v>134.615480348608</v>
+        <v>-661.182421383405</v>
       </c>
       <c r="E36" s="11">
         <f t="shared" si="8"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F36" s="9">
         <f t="shared" si="7"/>
-        <v>8948.69451965139</v>
+        <v>5661.18242138341</v>
       </c>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="9">
         <f t="shared" si="5"/>
-        <v>1540.82342959077</v>
+        <v>-57181.8905811293</v>
       </c>
       <c r="C37" s="7">
         <v>35</v>
       </c>
       <c r="D37" s="9">
         <f t="shared" si="6"/>
-        <v>19.7739006797483</v>
+        <v>-733.834262457825</v>
       </c>
       <c r="E37" s="11">
         <f t="shared" si="8"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F37" s="9">
         <f t="shared" si="7"/>
-        <v>9063.53609932025</v>
+        <v>5733.83426245783</v>
       </c>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="9">
         <f t="shared" si="5"/>
-        <v>-7522.71266972948</v>
+        <v>-62915.7248435871</v>
       </c>
       <c r="C38" s="7">
         <v>36</v>
       </c>
       <c r="D38" s="9">
         <f t="shared" si="6"/>
-        <v>-96.5414792615283</v>
+        <v>-807.418468826034</v>
       </c>
       <c r="E38" s="11">
         <f t="shared" si="8"/>
-        <v>9083.31</v>
+        <v>5000</v>
       </c>
       <c r="F38" s="9">
         <f t="shared" si="7"/>
-        <v>9179.85147926153</v>
+        <v>5807.41846882603</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5">
+      <c r="B39" s="8">
+        <v>100000</v>
+      </c>
+      <c r="D39" s="2">
+        <f>SUM(D3:D38)</f>
+        <v>11276.8566875869</v>
+      </c>
+      <c r="E39" s="1">
+        <f>SUM(E3:E38)</f>
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="1">
+        <f>E39-B39</f>
+        <v>80000</v>
+      </c>
+      <c r="D44" s="2">
+        <f>C44-15866</f>
+        <v>64134</v>
+      </c>
+    </row>
+    <row r="46" ht="57.6" spans="5:5">
+      <c r="E46" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
